--- a/Result/profitability/2103.xlsx
+++ b/Result/profitability/2103.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.32875</v>
+        <v>0.49125</v>
       </c>
       <c r="N2" t="n">
-        <v>11.31125</v>
+        <v>12.63875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,16 +681,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0.455</v>
+        <v>0.6824999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>12.625</v>
+        <v>14.0325</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,16 +792,16 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.41</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6425</v>
+        <v>0.80875</v>
       </c>
       <c r="N4" t="n">
-        <v>13.9725</v>
+        <v>15.18125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6174999999999999</v>
+        <v>0.84375</v>
       </c>
       <c r="N5" t="n">
-        <v>11.56875</v>
+        <v>13.17125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.66</v>
       </c>
       <c r="M6" t="n">
-        <v>0.71</v>
+        <v>0.93875</v>
       </c>
       <c r="N6" t="n">
-        <v>13.4775</v>
+        <v>14.98375</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,13 +1155,13 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>1.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0.86625</v>
+        <v>1.04125</v>
       </c>
       <c r="N7" t="n">
-        <v>16.33625</v>
+        <v>17.7225</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.78</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9225</v>
+        <v>1.0725</v>
       </c>
       <c r="N8" t="n">
-        <v>17.41375</v>
+        <v>18.52625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11881</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9368</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2513</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1811</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>340</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2151</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1431</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.59875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.264150943396226</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.899999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.7265306122448978</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-22.625</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.539015606242497</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
